--- a/docs/technical/SalesVerse-2.0-Data-Dictionary.xlsx
+++ b/docs/technical/SalesVerse-2.0-Data-Dictionary.xlsx
@@ -19661,7 +19661,7 @@
       </c>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>Values before the change. Passwords, hashes, encrypted identifiers, tokens and storage keys are written as [REDACTED].</t>
+          <t>Values before the change. Passwords, hashes, encrypted identifiers, tokens and storage keys are written as a fixed REDACTED marker.</t>
         </is>
       </c>
     </row>
